--- a/docs/d/70/inyear.xlsx
+++ b/docs/d/70/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 78 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 75 clubs short</t>
         </is>
       </c>
     </row>
@@ -2148,8 +2148,8 @@
       <c r="W14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X14" s="9" t="n">
-        <v>0</v>
+      <c r="X14" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y14" s="9" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2964,8 +2964,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -16807,7 +16807,7 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -16877,8 +16877,8 @@
       <c r="Y161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z161" s="9" t="n">
-        <v>0</v>
+      <c r="Z161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA161" s="10" t="n">
         <v>1</v>
@@ -25044,7 +25044,7 @@
         </is>
       </c>
       <c r="E242" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F242" s="6" t="n">
         <v>10</v>
@@ -25114,8 +25114,8 @@
       <c r="Y242" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z242" s="9" t="n">
-        <v>0</v>
+      <c r="Z242" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA242" s="10" t="n">
         <v>1</v>
@@ -26432,7 +26432,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -27323,7 +27323,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -27884,7 +27884,7 @@
         <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>

--- a/docs/d/70/inyear.xlsx
+++ b/docs/d/70/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,11 @@
       <c r="AB25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3490,7 +3494,11 @@
       <c r="AB27" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC27" s="4" t="inlineStr"/>
+      <c r="AC27" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -3999,7 +4007,11 @@
       <c r="AB32" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4403,7 +4415,11 @@
       <c r="AB36" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC36" s="4" t="inlineStr"/>
+      <c r="AC36" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -16680,7 +16696,11 @@
       <c r="AB159" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC159" s="4" t="inlineStr"/>
+      <c r="AC159" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -17298,7 +17318,11 @@
       <c r="AB165" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC165" s="4" t="inlineStr"/>
+      <c r="AC165" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -17706,7 +17730,11 @@
       <c r="AB169" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC169" s="4" t="inlineStr"/>
+      <c r="AC169" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -17807,7 +17835,11 @@
       <c r="AB170" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC170" s="4" t="inlineStr"/>
+      <c r="AC170" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -18009,7 +18041,11 @@
       <c r="AB172" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC172" s="4" t="inlineStr"/>
+      <c r="AC172" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -18211,7 +18247,11 @@
       <c r="AB174" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC174" s="4" t="inlineStr"/>
+      <c r="AC174" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -21099,7 +21139,11 @@
       <c r="AB202" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC202" s="4" t="inlineStr"/>
+      <c r="AC202" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -21406,7 +21450,11 @@
       <c r="AB205" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC205" s="4" t="inlineStr"/>
+      <c r="AC205" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -23042,7 +23090,11 @@
       <c r="AB221" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC221" s="4" t="inlineStr"/>
+      <c r="AC221" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="4" t="inlineStr">

--- a/docs/d/70/inyear.xlsx
+++ b/docs/d/70/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 75 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 67 clubs short</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1106,8 +1106,8 @@
       <c r="S4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="9" t="n">
-        <v>0</v>
+      <c r="T4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U4" s="9" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
         <v>2</v>
       </c>
       <c r="R25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="9" t="n">
         <v>0</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4511,8 +4511,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6639,13 +6639,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6695,8 +6695,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -9936,7 +9936,7 @@
         <v>0</v>
       </c>
       <c r="Q92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" s="9" t="n">
         <v>0</v>
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10358,8 +10358,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10824,10 +10824,10 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
@@ -10838,8 +10838,8 @@
       <c r="T101" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U101" s="9" t="n">
-        <v>0</v>
+      <c r="U101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V101" s="10" t="n">
         <v>4</v>
@@ -11710,7 +11710,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11780,8 +11780,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -13136,7 +13136,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13206,8 +13206,8 @@
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -15423,7 +15423,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -15437,13 +15437,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -15484,8 +15484,8 @@
       <c r="V147" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W147" s="9" t="n">
-        <v>2</v>
+      <c r="W147" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X147" s="10" t="n">
         <v>5</v>
@@ -16215,7 +16215,7 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16285,8 +16285,8 @@
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="9" t="n">
-        <v>0</v>
+      <c r="Z155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA155" s="10" t="n">
         <v>1</v>
@@ -16827,7 +16827,7 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -16879,8 +16879,8 @@
       <c r="S161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T161" s="9" t="n">
-        <v>0</v>
+      <c r="T161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U161" s="9" t="n">
         <v>0</v>
@@ -18681,7 +18681,7 @@
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18695,13 +18695,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
@@ -18733,14 +18733,14 @@
       <c r="S179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T179" s="9" t="n">
-        <v>0</v>
+      <c r="T179" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U179" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V179" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W179" s="9" t="n">
         <v>0</v>
@@ -18751,8 +18751,8 @@
       <c r="Y179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z179" s="9" t="n">
-        <v>0</v>
+      <c r="Z179" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA179" s="10" t="n">
         <v>1</v>
@@ -21165,7 +21165,7 @@
         </is>
       </c>
       <c r="E203" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F203" s="6" t="n">
         <v>10</v>
@@ -21220,8 +21220,8 @@
       <c r="T203" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U203" s="9" t="n">
-        <v>0</v>
+      <c r="U203" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V203" s="9" t="n">
         <v>1</v>
@@ -23163,7 +23163,7 @@
         <v>2</v>
       </c>
       <c r="R222" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S222" s="9" t="n">
         <v>0</v>
@@ -24219,13 +24219,13 @@
         </is>
       </c>
       <c r="I233" s="4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J233" s="4" t="n">
         <v>52</v>
       </c>
       <c r="K233" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L233" s="4" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>0</v>
       </c>
       <c r="V233" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W233" s="9" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         </is>
       </c>
       <c r="E252" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F252" s="6" t="n">
         <v>10</v>
@@ -26138,8 +26138,8 @@
       <c r="S252" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T252" s="9" t="n">
-        <v>0</v>
+      <c r="T252" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U252" s="9" t="n">
         <v>0</v>
@@ -26185,7 +26185,7 @@
         </is>
       </c>
       <c r="E253" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F253" s="6" t="n">
         <v>10</v>
@@ -26255,8 +26255,8 @@
       <c r="Y253" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z253" s="9" t="n">
-        <v>0</v>
+      <c r="Z253" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA253" s="10" t="n">
         <v>1</v>
@@ -26352,7 +26352,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -26550,7 +26550,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -26682,7 +26682,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -26913,7 +26913,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -26946,7 +26946,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -27012,7 +27012,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -27111,7 +27111,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -27276,7 +27276,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -27342,7 +27342,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -27375,7 +27375,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -27507,7 +27507,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -27705,7 +27705,7 @@
         <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -28002,7 +28002,7 @@
         <v>5</v>
       </c>
       <c r="D52" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>

--- a/docs/d/70/inyear.xlsx
+++ b/docs/d/70/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 67 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 46 clubs short</t>
         </is>
       </c>
     </row>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="9" t="n">
         <v>1</v>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3380,8 +3380,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -3429,13 +3429,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>4</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>6</v>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3897,8 +3897,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="P32" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q32" s="9" t="n">
         <v>1</v>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4612,8 +4612,8 @@
       <c r="Y38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" s="9" t="n">
-        <v>0</v>
+      <c r="Z38" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA38" s="10" t="n">
         <v>1</v>
@@ -5309,8 +5309,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="9" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5507,8 +5507,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5882,8 +5882,8 @@
       <c r="R51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S51" s="9" t="n">
-        <v>1</v>
+      <c r="S51" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T51" s="10" t="n">
         <v>1</v>
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6596,8 +6596,8 @@
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8180,8 +8180,8 @@
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -8556,7 +8556,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" s="10" t="n">
         <v>1</v>
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8774,8 +8774,8 @@
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -9793,7 +9793,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9863,8 +9863,8 @@
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -12829,7 +12829,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12899,8 +12899,8 @@
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -14433,7 +14433,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14503,8 +14503,8 @@
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="9" t="n">
-        <v>0</v>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
@@ -14829,7 +14829,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14899,8 +14899,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -15720,7 +15720,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15790,8 +15790,8 @@
       <c r="Y150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z150" s="9" t="n">
-        <v>0</v>
+      <c r="Z150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA150" s="10" t="n">
         <v>1</v>
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15889,8 +15889,8 @@
       <c r="Y151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z151" s="9" t="n">
-        <v>0</v>
+      <c r="Z151" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA151" s="10" t="n">
         <v>1</v>
@@ -16116,7 +16116,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -16186,8 +16186,8 @@
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="9" t="n">
-        <v>0</v>
+      <c r="Z154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA154" s="10" t="n">
         <v>1</v>
@@ -16658,13 +16658,13 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q159" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R159" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S159" s="10" t="n">
         <v>2</v>
@@ -18067,7 +18067,7 @@
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>10</v>
@@ -18137,8 +18137,8 @@
       <c r="Y173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z173" s="9" t="n">
-        <v>0</v>
+      <c r="Z173" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA173" s="10" t="n">
         <v>1</v>
@@ -18479,7 +18479,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -18549,8 +18549,8 @@
       <c r="Y177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z177" s="9" t="n">
-        <v>0</v>
+      <c r="Z177" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA177" s="10" t="n">
         <v>1</v>
@@ -19610,7 +19610,7 @@
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>10</v>
@@ -19680,8 +19680,8 @@
       <c r="Y188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z188" s="9" t="n">
-        <v>0</v>
+      <c r="Z188" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA188" s="10" t="n">
         <v>1</v>
@@ -20236,7 +20236,7 @@
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" s="6" t="n">
         <v>10</v>
@@ -20306,8 +20306,8 @@
       <c r="Y194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z194" s="9" t="n">
-        <v>0</v>
+      <c r="Z194" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA194" s="10" t="n">
         <v>1</v>
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="P195" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q195" s="9" t="n">
         <v>0</v>
@@ -22745,7 +22745,7 @@
         </is>
       </c>
       <c r="P218" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q218" s="9" t="n">
         <v>0</v>
@@ -23116,7 +23116,7 @@
         </is>
       </c>
       <c r="E222" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F222" s="6" t="n">
         <v>10</v>
@@ -23162,8 +23162,8 @@
       <c r="Q222" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R222" s="9" t="n">
-        <v>1</v>
+      <c r="R222" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S222" s="9" t="n">
         <v>0</v>
@@ -24354,7 +24354,7 @@
         <v>0</v>
       </c>
       <c r="S234" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T234" s="10" t="n">
         <v>1</v>
@@ -24601,7 +24601,7 @@
         </is>
       </c>
       <c r="E237" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F237" s="6" t="n">
         <v>10</v>
@@ -24671,8 +24671,8 @@
       <c r="Y237" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z237" s="9" t="n">
-        <v>0</v>
+      <c r="Z237" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA237" s="10" t="n">
         <v>1</v>
@@ -25245,7 +25245,7 @@
         <v>0</v>
       </c>
       <c r="S243" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T243" s="10" t="n">
         <v>1</v>
@@ -25690,7 +25690,7 @@
         </is>
       </c>
       <c r="E248" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F248" s="6" t="n">
         <v>10</v>
@@ -25760,8 +25760,8 @@
       <c r="Y248" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z248" s="9" t="n">
-        <v>0</v>
+      <c r="Z248" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA248" s="10" t="n">
         <v>1</v>
@@ -25833,7 +25833,7 @@
         <v>1</v>
       </c>
       <c r="Q249" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R249" s="9" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         </is>
       </c>
       <c r="E252" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F252" s="6" t="n">
         <v>10</v>
@@ -26141,8 +26141,8 @@
       <c r="T252" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U252" s="9" t="n">
-        <v>0</v>
+      <c r="U252" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V252" s="9" t="n">
         <v>1</v>
@@ -26484,7 +26484,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -26517,7 +26517,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -26550,7 +26550,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -26616,7 +26616,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -26649,7 +26649,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -26682,7 +26682,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -26781,7 +26781,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -26814,7 +26814,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -26913,7 +26913,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -27078,7 +27078,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -27210,7 +27210,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -27243,7 +27243,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -27309,7 +27309,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -27342,7 +27342,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -27474,7 +27474,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -27507,7 +27507,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -27573,7 +27573,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -27606,7 +27606,7 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -27837,13 +27837,13 @@
         <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -27903,7 +27903,7 @@
         <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -28002,7 +28002,7 @@
         <v>5</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>

--- a/docs/d/70/inyear.xlsx
+++ b/docs/d/70/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 46 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 46 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1068,17 +1068,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="8" t="n">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1514,8 +1514,8 @@
       <c r="S8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="9" t="n">
-        <v>0</v>
+      <c r="T8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U8" s="9" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>4</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>7</v>
@@ -1581,17 +1581,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1629,7 +1629,7 @@
         <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>4</v>
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1888,17 +1888,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1993,17 +1993,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M13" s="8" t="n">
@@ -2134,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="9" t="n">
         <v>0</v>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2399,17 +2399,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="8" t="n">
@@ -2443,8 +2443,8 @@
       <c r="U17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="9" t="n">
-        <v>3</v>
+      <c r="V17" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2504,13 +2504,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2706,17 +2706,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M20" s="8" t="n">
@@ -2750,8 +2750,8 @@
       <c r="U20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="9" t="n">
-        <v>2</v>
+      <c r="V20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2807,13 +2807,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2908,17 +2908,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="8" t="n">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>6</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3219,13 +3219,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3263,11 +3263,11 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>0</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>7</v>
@@ -3324,17 +3324,17 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M26" s="8" t="n">
@@ -3429,13 +3429,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3572,8 +3572,8 @@
       <c r="S28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T28" s="9" t="n">
-        <v>0</v>
+      <c r="T28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U28" s="9" t="n">
         <v>0</v>
@@ -3635,17 +3635,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3841,13 +3841,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3942,17 +3942,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M32" s="8" t="n">
@@ -3990,7 +3990,7 @@
         <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>7</v>
@@ -4047,13 +4047,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4287,8 +4287,8 @@
       <c r="S35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T35" s="9" t="n">
-        <v>0</v>
+      <c r="T35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U35" s="9" t="n">
         <v>0</v>
@@ -4296,8 +4296,8 @@
       <c r="V35" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W35" s="9" t="n">
-        <v>2</v>
+      <c r="W35" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X35" s="10" t="n">
         <v>6</v>
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4350,13 +4350,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4394,8 +4394,8 @@
       <c r="U36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="9" t="n">
-        <v>0</v>
+      <c r="V36" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4455,13 +4455,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4556,13 +4556,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4657,17 +4657,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4758,13 +4758,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="P40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>0</v>
@@ -4857,13 +4857,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4956,13 +4956,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5055,17 +5055,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -5100,7 +5100,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -5154,13 +5154,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5253,17 +5253,17 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M45" s="8" t="n">
@@ -5297,11 +5297,11 @@
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="9" t="n">
-        <v>3</v>
+      <c r="V45" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" s="9" t="n">
         <v>0</v>
@@ -5352,17 +5352,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5451,13 +5451,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5550,13 +5550,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5649,17 +5649,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-19</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5748,13 +5748,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5847,17 +5847,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M51" s="8" t="n">
@@ -5876,8 +5876,8 @@
       <c r="P51" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q51" s="9" t="n">
-        <v>1</v>
+      <c r="Q51" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R51" s="9" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5946,17 +5946,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6045,17 +6045,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M53" s="8" t="n">
@@ -6092,8 +6092,8 @@
       <c r="V53" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W53" s="9" t="n">
-        <v>2</v>
+      <c r="W53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X53" s="10" t="n">
         <v>4</v>
@@ -6144,17 +6144,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -6243,13 +6243,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6342,13 +6342,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6488,8 +6488,8 @@
       <c r="V57" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W57" s="9" t="n">
-        <v>2</v>
+      <c r="W57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>4</v>
@@ -6540,13 +6540,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6639,17 +6639,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6738,17 +6738,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
@@ -6782,11 +6782,11 @@
       <c r="U60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V60" s="9" t="n">
-        <v>3</v>
+      <c r="V60" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>4</v>
@@ -6837,13 +6837,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6936,17 +6936,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7134,13 +7134,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>0</v>
@@ -7233,13 +7233,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -7332,13 +7332,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7431,13 +7431,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7530,13 +7530,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7629,13 +7629,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7728,13 +7728,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7827,17 +7827,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="8" t="n">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>0</v>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8025,17 +8025,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -8052,7 +8052,7 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="9" t="n">
         <v>1</v>
@@ -8061,7 +8061,7 @@
         <v>0</v>
       </c>
       <c r="S73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" s="9" t="n">
         <v>0</v>
@@ -8069,8 +8069,8 @@
       <c r="U73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="9" t="n">
-        <v>2</v>
+      <c r="V73" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8124,17 +8124,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -8169,7 +8169,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8223,13 +8223,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="P75" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q75" s="9" t="n">
         <v>1</v>
@@ -8259,7 +8259,7 @@
         <v>0</v>
       </c>
       <c r="S75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" s="9" t="n">
         <v>0</v>
@@ -8268,7 +8268,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8322,13 +8322,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8421,13 +8421,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8520,13 +8520,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8619,17 +8619,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
@@ -8718,13 +8718,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8817,13 +8817,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -8916,13 +8916,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>0</v>
       </c>
       <c r="S82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T82" s="9" t="n">
         <v>0</v>
@@ -9015,13 +9015,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9114,13 +9114,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9158,8 +9158,8 @@
       <c r="U84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="9" t="n">
-        <v>3</v>
+      <c r="V84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9213,17 +9213,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>5</v>
@@ -9411,13 +9411,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9510,13 +9510,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9609,13 +9609,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9708,13 +9708,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9807,13 +9807,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9906,17 +9906,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -10005,13 +10005,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10104,17 +10104,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M94" s="8" t="n">
@@ -10139,8 +10139,8 @@
       <c r="R94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S94" s="9" t="n">
-        <v>1</v>
+      <c r="S94" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T94" s="9" t="n">
         <v>0</v>
@@ -10203,17 +10203,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -10302,13 +10302,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10401,17 +10401,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10500,13 +10500,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>4</v>
@@ -10599,13 +10599,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10698,13 +10698,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10797,17 +10797,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -10896,13 +10896,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>11</v>
+        <v>-7</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>4</v>
       </c>
       <c r="W102" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>7</v>
@@ -11001,17 +11001,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -11102,17 +11102,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -11207,13 +11207,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11308,13 +11308,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11409,13 +11409,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q107" s="9" t="n">
         <v>0</v>
@@ -11454,7 +11454,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11500,7 +11500,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11514,17 +11514,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L108" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11558,11 +11558,11 @@
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V108" s="9" t="n">
+      <c r="V108" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W108" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W108" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>7</v>
@@ -11619,17 +11619,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
@@ -11724,13 +11724,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11825,17 +11825,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -11870,7 +11870,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -11930,13 +11930,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12031,17 +12031,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -12132,13 +12132,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12233,13 +12233,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12334,13 +12334,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12435,13 +12435,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12536,17 +12536,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q118" s="9" t="n">
         <v>0</v>
@@ -12572,7 +12572,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118" s="9" t="n">
         <v>0</v>
@@ -12641,13 +12641,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12742,13 +12742,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12843,13 +12843,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12948,13 +12948,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13049,13 +13049,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13150,13 +13150,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -13251,13 +13251,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13352,13 +13352,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -13396,11 +13396,11 @@
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="9" t="n">
+      <c r="V126" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W126" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W126" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>4</v>
@@ -13457,13 +13457,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13556,17 +13556,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L128" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M128" s="8" t="n">
@@ -13655,17 +13655,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -13754,17 +13754,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
@@ -13853,13 +13853,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -13952,13 +13952,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -14051,13 +14051,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14150,13 +14150,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -14194,11 +14194,11 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="9" t="n">
-        <v>1</v>
+      <c r="V134" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W134" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X134" s="9" t="n">
         <v>1</v>
@@ -14249,13 +14249,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14348,13 +14348,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>0</v>
       </c>
       <c r="V137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
@@ -14532,7 +14532,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14546,13 +14546,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="P138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q138" s="9" t="n">
         <v>1</v>
@@ -14590,8 +14590,8 @@
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="9" t="n">
-        <v>3</v>
+      <c r="V138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -14645,13 +14645,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -14744,13 +14744,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14843,13 +14843,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q142" s="9" t="n">
         <v>0</v>
@@ -14987,7 +14987,7 @@
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -15041,13 +15041,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15140,13 +15140,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15239,13 +15239,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15338,13 +15338,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15437,17 +15437,17 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L147" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L147" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M147" s="8" t="n">
@@ -15536,13 +15536,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15734,13 +15734,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -15833,13 +15833,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>0</v>
       </c>
       <c r="X152" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y152" s="9" t="n">
         <v>0</v>
@@ -16031,13 +16031,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -16229,13 +16229,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>0</v>
       </c>
       <c r="V155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W155" s="9" t="n">
         <v>0</v>
@@ -16328,13 +16328,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -16427,13 +16427,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>0</v>
       </c>
       <c r="V157" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
@@ -16526,17 +16526,17 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L158" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L158" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M158" s="8" t="n">
@@ -16631,13 +16631,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>4</v>
       </c>
       <c r="W159" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X159" s="10" t="n">
         <v>7</v>
@@ -16736,13 +16736,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
@@ -16841,13 +16841,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -17047,17 +17047,17 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L163" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L163" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M163" s="8" t="n">
@@ -17148,17 +17148,17 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L164" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L164" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M164" s="8" t="n">
@@ -17253,13 +17253,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
@@ -17358,17 +17358,17 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L166" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L166" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M166" s="8" t="n">
@@ -17463,17 +17463,17 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L167" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M167" s="8" t="n">
@@ -17511,7 +17511,7 @@
         <v>4</v>
       </c>
       <c r="W167" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X167" s="10" t="n">
         <v>6</v>
@@ -17564,13 +17564,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>0</v>
       </c>
       <c r="V168" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W168" s="9" t="n">
         <v>0</v>
@@ -17665,13 +17665,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>6</v>
+        <v>-8</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>10</v>
@@ -17770,13 +17770,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
@@ -17802,8 +17802,8 @@
       <c r="Q170" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R170" s="9" t="n">
-        <v>1</v>
+      <c r="R170" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S170" s="9" t="n">
         <v>1</v>
@@ -17818,7 +17818,7 @@
         <v>4</v>
       </c>
       <c r="W170" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X170" s="10" t="n">
         <v>5</v>
@@ -17875,13 +17875,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
@@ -17976,13 +17976,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
@@ -18081,13 +18081,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -18182,13 +18182,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
@@ -18220,8 +18220,8 @@
       <c r="S174" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T174" s="9" t="n">
-        <v>0</v>
+      <c r="T174" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U174" s="9" t="n">
         <v>0</v>
@@ -18273,7 +18273,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18287,13 +18287,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         </is>
       </c>
       <c r="P175" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q175" s="9" t="n">
         <v>0</v>
@@ -18331,8 +18331,8 @@
       <c r="U175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V175" s="9" t="n">
-        <v>3</v>
+      <c r="V175" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W175" s="9" t="n">
         <v>0</v>
@@ -18388,17 +18388,17 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L176" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L176" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M176" s="8" t="n">
@@ -18493,13 +18493,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -18594,13 +18594,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L178" s="7" t="inlineStr">
         <is>
@@ -18695,13 +18695,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
@@ -18800,13 +18800,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>0</v>
       </c>
       <c r="V180" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W180" s="9" t="n">
         <v>0</v>
@@ -18901,17 +18901,17 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L181" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L181" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M181" s="8" t="n">
@@ -18988,7 +18988,7 @@
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>10</v>
@@ -19002,13 +19002,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
@@ -19043,8 +19043,8 @@
       <c r="T182" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U182" s="9" t="n">
-        <v>0</v>
+      <c r="U182" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V182" s="9" t="n">
         <v>2</v>
@@ -19103,13 +19103,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
@@ -19208,17 +19208,17 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L184" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L184" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M184" s="8" t="n">
@@ -19313,13 +19313,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>10</v>
@@ -19414,13 +19414,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
@@ -19458,8 +19458,8 @@
       <c r="U186" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V186" s="9" t="n">
-        <v>3</v>
+      <c r="V186" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W186" s="9" t="n">
         <v>0</v>
@@ -19505,7 +19505,7 @@
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -19563,11 +19563,11 @@
       <c r="U187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V187" s="9" t="n">
-        <v>2</v>
+      <c r="V187" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W187" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X187" s="10" t="n">
         <v>5</v>
@@ -19624,13 +19624,13 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L188" s="7" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>10</v>
@@ -19725,13 +19725,13 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
@@ -19769,8 +19769,8 @@
       <c r="U189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V189" s="9" t="n">
-        <v>3</v>
+      <c r="V189" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W189" s="9" t="n">
         <v>0</v>
@@ -19830,13 +19830,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L190" s="7" t="inlineStr">
         <is>
@@ -19935,17 +19935,17 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L191" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L191" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M191" s="8" t="n">
@@ -20040,13 +20040,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L192" s="7" t="inlineStr">
         <is>
@@ -20145,17 +20145,17 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L193" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L193" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M193" s="8" t="n">
@@ -20351,13 +20351,13 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>1</v>
       </c>
       <c r="Q195" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R195" s="9" t="n">
         <v>0</v>
@@ -20456,13 +20456,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L196" s="7" t="inlineStr">
         <is>
@@ -20557,17 +20557,17 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L197" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L197" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M197" s="8" t="n">
@@ -20662,13 +20662,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L198" s="7" t="inlineStr">
         <is>
@@ -20763,13 +20763,13 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L199" s="4" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         </is>
       </c>
       <c r="E200" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F200" s="6" t="n">
         <v>10</v>
@@ -20915,8 +20915,8 @@
       <c r="V200" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W200" s="9" t="n">
-        <v>3</v>
+      <c r="W200" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X200" s="10" t="n">
         <v>4</v>
@@ -20955,7 +20955,7 @@
         </is>
       </c>
       <c r="E201" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F201" s="6" t="n">
         <v>10</v>
@@ -20969,13 +20969,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
@@ -21007,8 +21007,8 @@
       <c r="S201" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T201" s="9" t="n">
-        <v>0</v>
+      <c r="T201" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U201" s="9" t="n">
         <v>0</v>
@@ -21074,13 +21074,13 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K202" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
@@ -21284,13 +21284,13 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K204" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L204" s="7" t="inlineStr">
         <is>
@@ -21385,13 +21385,13 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K205" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
@@ -21490,13 +21490,13 @@
         </is>
       </c>
       <c r="I206" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J206" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K206" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L206" s="7" t="inlineStr">
         <is>
@@ -21591,13 +21591,13 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J207" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K207" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L207" s="7" t="inlineStr">
         <is>
@@ -21692,13 +21692,13 @@
         </is>
       </c>
       <c r="I208" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J208" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K208" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L208" s="7" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>0</v>
       </c>
       <c r="V208" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W208" s="9" t="n">
         <v>0</v>
@@ -21793,13 +21793,13 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J209" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K209" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
@@ -21894,13 +21894,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J210" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L210" s="7" t="inlineStr">
         <is>
@@ -21995,13 +21995,13 @@
         </is>
       </c>
       <c r="I211" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J211" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K211" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L211" s="4" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>0</v>
       </c>
       <c r="V211" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W211" s="9" t="n">
         <v>0</v>
@@ -22082,7 +22082,7 @@
         </is>
       </c>
       <c r="E212" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F212" s="6" t="n">
         <v>10</v>
@@ -22096,13 +22096,13 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J212" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K212" s="4" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
@@ -22143,8 +22143,8 @@
       <c r="V212" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W212" s="9" t="n">
-        <v>2</v>
+      <c r="W212" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X212" s="10" t="n">
         <v>5</v>
@@ -22302,13 +22302,13 @@
         </is>
       </c>
       <c r="I214" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J214" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K214" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L214" s="7" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>0</v>
       </c>
       <c r="V214" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W214" s="9" t="n">
         <v>0</v>
@@ -22407,13 +22407,13 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J215" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K215" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
@@ -22512,17 +22512,17 @@
         </is>
       </c>
       <c r="I216" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J216" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K216" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L216" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L216" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M216" s="8" t="n">
@@ -22617,13 +22617,13 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K217" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>0</v>
       </c>
       <c r="V217" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W217" s="9" t="n">
         <v>0</v>
@@ -22718,13 +22718,13 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K218" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>2</v>
       </c>
       <c r="Q218" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R218" s="9" t="n">
         <v>0</v>
@@ -22823,13 +22823,13 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J219" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K219" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L219" s="7" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>0</v>
       </c>
       <c r="V220" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W220" s="9" t="n">
         <v>0</v>
@@ -23025,13 +23025,13 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J221" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K221" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L221" s="4" t="inlineStr">
         <is>
@@ -23130,13 +23130,13 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J222" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K222" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
@@ -23229,13 +23229,13 @@
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J223" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K223" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L223" s="7" t="inlineStr">
         <is>
@@ -23328,13 +23328,13 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J224" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K224" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L224" s="7" t="inlineStr">
         <is>
@@ -23427,13 +23427,13 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J225" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K225" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L225" s="7" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         </is>
       </c>
       <c r="E226" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F226" s="6" t="n">
         <v>10</v>
@@ -23526,13 +23526,13 @@
         </is>
       </c>
       <c r="I226" s="4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J226" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K226" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
@@ -23573,8 +23573,8 @@
       <c r="V226" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W226" s="9" t="n">
-        <v>1</v>
+      <c r="W226" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X226" s="10" t="n">
         <v>7</v>
@@ -23625,13 +23625,13 @@
         </is>
       </c>
       <c r="I227" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J227" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K227" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L227" s="7" t="inlineStr">
         <is>
@@ -23724,13 +23724,13 @@
         </is>
       </c>
       <c r="I228" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J228" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K228" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>1</v>
       </c>
       <c r="V228" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W228" s="9" t="n">
         <v>0</v>
@@ -23823,13 +23823,13 @@
         </is>
       </c>
       <c r="I229" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K229" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L229" s="7" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         </is>
       </c>
       <c r="E230" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F230" s="6" t="n">
         <v>10</v>
@@ -23922,13 +23922,13 @@
         </is>
       </c>
       <c r="I230" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J230" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K230" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
@@ -23963,8 +23963,8 @@
       <c r="T230" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U230" s="9" t="n">
-        <v>0</v>
+      <c r="U230" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V230" s="9" t="n">
         <v>1</v>
@@ -24021,13 +24021,13 @@
         </is>
       </c>
       <c r="I231" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J231" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K231" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L231" s="4" t="inlineStr">
         <is>
@@ -24120,13 +24120,13 @@
         </is>
       </c>
       <c r="I232" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J232" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K232" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L232" s="7" t="inlineStr">
         <is>
@@ -24219,13 +24219,13 @@
         </is>
       </c>
       <c r="I233" s="4" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="J233" s="4" t="n">
         <v>52</v>
       </c>
       <c r="K233" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L233" s="4" t="inlineStr">
         <is>
@@ -24318,13 +24318,13 @@
         </is>
       </c>
       <c r="I234" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K234" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L234" s="7" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         </is>
       </c>
       <c r="E235" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F235" s="6" t="n">
         <v>10</v>
@@ -24417,13 +24417,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J235" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L235" s="7" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         </is>
       </c>
       <c r="P235" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q235" s="9" t="n">
         <v>0</v>
@@ -24458,8 +24458,8 @@
       <c r="T235" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U235" s="9" t="n">
-        <v>0</v>
+      <c r="U235" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V235" s="9" t="n">
         <v>1</v>
@@ -24615,13 +24615,13 @@
         </is>
       </c>
       <c r="I237" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J237" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K237" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L237" s="7" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>0</v>
       </c>
       <c r="V237" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W237" s="9" t="n">
         <v>0</v>
@@ -24813,13 +24813,13 @@
         </is>
       </c>
       <c r="I239" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J239" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K239" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L239" s="7" t="inlineStr">
         <is>
@@ -24912,13 +24912,13 @@
         </is>
       </c>
       <c r="I240" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J240" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K240" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L240" s="7" t="inlineStr">
         <is>
@@ -25011,13 +25011,13 @@
         </is>
       </c>
       <c r="I241" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K241" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L241" s="7" t="inlineStr">
         <is>
@@ -25110,13 +25110,13 @@
         </is>
       </c>
       <c r="I242" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J242" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K242" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L242" s="7" t="inlineStr">
         <is>
@@ -25209,13 +25209,13 @@
         </is>
       </c>
       <c r="I243" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J243" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K243" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L243" s="7" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         </is>
       </c>
       <c r="P243" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q243" s="9" t="n">
         <v>0</v>
@@ -25254,7 +25254,7 @@
         <v>1</v>
       </c>
       <c r="V243" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W243" s="9" t="n">
         <v>0</v>
@@ -25407,13 +25407,13 @@
         </is>
       </c>
       <c r="I245" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J245" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K245" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L245" s="7" t="inlineStr">
         <is>
@@ -25506,17 +25506,17 @@
         </is>
       </c>
       <c r="I246" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J246" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K246" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L246" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L246" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M246" s="8" t="n">
@@ -25605,17 +25605,17 @@
         </is>
       </c>
       <c r="I247" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J247" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K247" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L247" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L247" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M247" s="8" t="n">
@@ -25704,13 +25704,13 @@
         </is>
       </c>
       <c r="I248" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K248" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L248" s="7" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>0</v>
       </c>
       <c r="V248" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W248" s="9" t="n">
         <v>0</v>
@@ -25803,17 +25803,17 @@
         </is>
       </c>
       <c r="I249" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J249" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K249" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L249" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L249" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M249" s="8" t="n">
@@ -25902,13 +25902,13 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K250" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L250" s="7" t="inlineStr">
         <is>
@@ -26001,17 +26001,17 @@
         </is>
       </c>
       <c r="I251" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J251" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K251" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L251" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L251" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M251" s="8" t="n">
@@ -26049,7 +26049,7 @@
         <v>4</v>
       </c>
       <c r="W251" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X251" s="10" t="n">
         <v>4</v>
@@ -26100,13 +26100,13 @@
         </is>
       </c>
       <c r="I252" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J252" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K252" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L252" s="7" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>1</v>
       </c>
       <c r="V252" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W252" s="9" t="n">
         <v>0</v>
@@ -26199,13 +26199,13 @@
         </is>
       </c>
       <c r="I253" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K253" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L253" s="7" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>0</v>
       </c>
       <c r="V253" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W253" s="9" t="n">
         <v>0</v>
@@ -26367,7 +26367,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26385,7 +26385,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26400,7 +26400,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -26418,7 +26418,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -26433,7 +26433,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -26451,7 +26451,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -26466,7 +26466,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -26484,7 +26484,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -26499,7 +26499,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -26517,7 +26517,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -26532,7 +26532,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -26550,7 +26550,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -26598,7 +26598,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -26616,7 +26616,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -26631,7 +26631,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -26649,7 +26649,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -26664,7 +26664,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -26682,7 +26682,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -26697,7 +26697,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -26730,7 +26730,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -26781,7 +26781,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -26796,7 +26796,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -26829,7 +26829,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -26847,7 +26847,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -26862,7 +26862,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -26913,7 +26913,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -26928,7 +26928,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -26961,7 +26961,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -26994,7 +26994,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -27012,7 +27012,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -27027,7 +27027,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -27060,7 +27060,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -27093,7 +27093,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -27111,7 +27111,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -27159,7 +27159,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -27177,7 +27177,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -27210,7 +27210,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -27291,7 +27291,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -27390,7 +27390,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -27423,7 +27423,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -27441,7 +27441,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -27456,7 +27456,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -27474,7 +27474,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -27489,7 +27489,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -27522,7 +27522,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -27540,7 +27540,7 @@
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -27555,7 +27555,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -27573,7 +27573,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -27621,7 +27621,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -27654,7 +27654,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -27672,7 +27672,7 @@
         <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -27771,7 +27771,7 @@
         <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -27786,7 +27786,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -27837,7 +27837,7 @@
         <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -27870,7 +27870,7 @@
         <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -27903,7 +27903,7 @@
         <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -27984,7 +27984,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">

--- a/docs/d/70/inyear.xlsx
+++ b/docs/d/70/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/70/inyear.xlsx
+++ b/docs/d/70/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/70/inyear.xlsx
+++ b/docs/d/70/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/70/inyear.xlsx
+++ b/docs/d/70/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/70/inyear.xlsx
+++ b/docs/d/70/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 46 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 46 clubs short</t>
         </is>
       </c>
     </row>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="9" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1917,8 +1917,8 @@
       <c r="P12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q12" s="9" t="n">
-        <v>1</v>
+      <c r="Q12" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>0</v>
@@ -2233,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" s="9" t="n">
         <v>0</v>
@@ -2504,13 +2504,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="10" t="n">
         <v>2</v>
@@ -3255,10 +3255,10 @@
         <v>1</v>
       </c>
       <c r="S25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U25" s="9" t="n">
         <v>0</v>
@@ -3429,13 +3429,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4278,8 +4278,8 @@
       <c r="P35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" s="9" t="n">
-        <v>1</v>
+      <c r="Q35" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>0</v>
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="P36" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q36" s="9" t="n">
         <v>1</v>
@@ -4556,13 +4556,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4657,13 +4657,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4758,13 +4758,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5099,8 +5099,8 @@
       <c r="U43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="9" t="n">
-        <v>3</v>
+      <c r="V43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5451,13 +5451,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5550,13 +5550,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="P50" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q50" s="9" t="n">
         <v>0</v>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5888,8 +5888,8 @@
       <c r="T51" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U51" s="9" t="n">
-        <v>0</v>
+      <c r="U51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V51" s="9" t="n">
         <v>1</v>
@@ -6144,17 +6144,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-23</v>
-      </c>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-9</v>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -6738,17 +6738,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L60" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7082,8 +7082,8 @@
       <c r="V63" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W63" s="9" t="n">
-        <v>2</v>
+      <c r="W63" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>7</v>
@@ -8916,13 +8916,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9015,13 +9015,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9906,13 +9906,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -9935,8 +9935,8 @@
       <c r="P92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" s="9" t="n">
-        <v>1</v>
+      <c r="Q92" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R92" s="9" t="n">
         <v>0</v>
@@ -9947,8 +9947,8 @@
       <c r="T92" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U92" s="9" t="n">
-        <v>0</v>
+      <c r="U92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V92" s="9" t="n">
         <v>1</v>
@@ -9991,7 +9991,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10005,13 +10005,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10043,8 +10043,8 @@
       <c r="S93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T93" s="9" t="n">
-        <v>0</v>
+      <c r="T93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U93" s="9" t="n">
         <v>0</v>
@@ -10302,13 +10302,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10401,13 +10401,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10500,13 +10500,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X98" s="10" t="n">
         <v>4</v>
@@ -10599,13 +10599,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="P102" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q102" s="10" t="n">
         <v>2</v>
@@ -10934,8 +10934,8 @@
       <c r="S102" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T102" s="9" t="n">
-        <v>0</v>
+      <c r="T102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U102" s="9" t="n">
         <v>0</v>
@@ -11001,13 +11001,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11514,13 +11514,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>4</v>
       </c>
       <c r="W108" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>7</v>
@@ -12067,7 +12067,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" s="9" t="n">
         <v>0</v>
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>0</v>
@@ -12334,13 +12334,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -13049,13 +13049,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="Q139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R139" s="9" t="n">
         <v>0</v>
@@ -14972,7 +14972,7 @@
         <v>1</v>
       </c>
       <c r="Q142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R142" s="9" t="n">
         <v>0</v>
@@ -15140,13 +15140,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15833,13 +15833,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -16031,13 +16031,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16456,8 +16456,8 @@
       <c r="P157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" s="9" t="n">
-        <v>1</v>
+      <c r="Q157" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R157" s="9" t="n">
         <v>0</v>
@@ -17253,13 +17253,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
@@ -17665,13 +17665,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -18182,13 +18182,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
@@ -18287,13 +18287,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
@@ -19935,13 +19935,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
@@ -20662,13 +20662,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L198" s="7" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>0</v>
       </c>
       <c r="V198" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W198" s="9" t="n">
         <v>0</v>
@@ -21880,7 +21880,7 @@
         </is>
       </c>
       <c r="E210" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F210" s="6" t="n">
         <v>10</v>
@@ -21935,8 +21935,8 @@
       <c r="T210" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U210" s="9" t="n">
-        <v>0</v>
+      <c r="U210" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V210" s="9" t="n">
         <v>1</v>
@@ -22096,13 +22096,13 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J212" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K212" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
@@ -22407,13 +22407,13 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J215" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K215" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>0</v>
       </c>
       <c r="V215" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W215" s="9" t="n">
         <v>0</v>
@@ -22617,13 +22617,13 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K217" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         </is>
       </c>
       <c r="P221" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q221" s="9" t="n">
         <v>0</v>
@@ -23526,13 +23526,13 @@
         </is>
       </c>
       <c r="I226" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J226" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K226" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         </is>
       </c>
       <c r="E231" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F231" s="6" t="n">
         <v>10</v>
@@ -24059,8 +24059,8 @@
       <c r="S231" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T231" s="9" t="n">
-        <v>0</v>
+      <c r="T231" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U231" s="9" t="n">
         <v>0</v>
@@ -24120,13 +24120,13 @@
         </is>
       </c>
       <c r="I232" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J232" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K232" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L232" s="7" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         </is>
       </c>
       <c r="E233" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F233" s="6" t="n">
         <v>10</v>
@@ -24249,19 +24249,19 @@
         <v>1</v>
       </c>
       <c r="Q233" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R233" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S233" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T233" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U233" s="9" t="n">
-        <v>0</v>
+      <c r="S233" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T233" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U233" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V233" s="9" t="n">
         <v>3</v>
@@ -25902,13 +25902,13 @@
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K250" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L250" s="7" t="inlineStr">
         <is>
@@ -26100,13 +26100,13 @@
         </is>
       </c>
       <c r="I252" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J252" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K252" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L252" s="7" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>1</v>
       </c>
       <c r="V252" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W252" s="9" t="n">
         <v>0</v>
@@ -26385,7 +26385,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26484,7 +26484,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -26550,13 +26550,13 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -26583,7 +26583,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -26649,13 +26649,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -26664,7 +26664,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -26697,7 +26697,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -26715,7 +26715,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -26913,7 +26913,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -26979,7 +26979,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -27342,7 +27342,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -27738,7 +27738,7 @@
         <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -27870,7 +27870,7 @@
         <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -27903,7 +27903,7 @@
         <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>

--- a/docs/d/70/inyear.xlsx
+++ b/docs/d/70/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 4 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 4 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 46 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 46 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -900,8 +900,8 @@
       <c r="S2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="9" t="n">
-        <v>0</v>
+      <c r="T2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U2" s="9" t="n">
         <v>0</v>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>4</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" s="10" t="n">
         <v>5</v>
@@ -2944,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" s="9" t="n">
         <v>0</v>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3114,17 +3114,17 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M24" s="8" t="n">
@@ -3161,8 +3161,8 @@
       <c r="V24" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W24" s="9" t="n">
-        <v>3</v>
+      <c r="W24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>6</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3246,13 +3246,13 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R25" s="9" t="n">
-        <v>1</v>
+      <c r="R25" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S25" s="9" t="n">
         <v>1</v>
@@ -3324,17 +3324,17 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M26" s="8" t="n">
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4379,8 +4379,8 @@
       <c r="P36" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" s="9" t="n">
-        <v>1</v>
+      <c r="Q36" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>0</v>
@@ -4455,13 +4455,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4956,13 +4956,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5154,13 +5154,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>0</v>
@@ -5550,13 +5550,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6083,8 +6083,8 @@
       <c r="S53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T53" s="9" t="n">
-        <v>0</v>
+      <c r="T53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U53" s="9" t="n">
         <v>0</v>
@@ -6441,13 +6441,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>4</v>
       </c>
       <c r="W57" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>4</v>
@@ -6837,13 +6837,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>0</v>
@@ -7629,13 +7629,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7728,13 +7728,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8025,17 +8025,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L73" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -8060,8 +8060,8 @@
       <c r="R73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S73" s="9" t="n">
-        <v>1</v>
+      <c r="S73" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T73" s="9" t="n">
         <v>0</v>
@@ -9051,7 +9051,7 @@
         <v>0</v>
       </c>
       <c r="S83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T83" s="10" t="n">
         <v>1</v>
@@ -9213,13 +9213,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9411,13 +9411,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9906,13 +9906,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10797,17 +10797,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L101" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -10845,7 +10845,7 @@
         <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>6</v>
@@ -10896,13 +10896,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>4</v>
       </c>
       <c r="W102" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X102" s="10" t="n">
         <v>7</v>
@@ -11102,13 +11102,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11825,13 +11825,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11869,8 +11869,8 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>3</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -12269,7 +12269,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T115" s="9" t="n">
         <v>0</v>
@@ -12334,13 +12334,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12435,13 +12435,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12641,13 +12641,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12679,8 +12679,8 @@
       <c r="S119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T119" s="9" t="n">
-        <v>0</v>
+      <c r="T119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U119" s="9" t="n">
         <v>0</v>
@@ -12742,13 +12742,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -13150,13 +13150,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13853,13 +13853,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -14549,10 +14549,10 @@
         <v>21</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         </is>
       </c>
       <c r="P157" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q157" s="10" t="n">
         <v>2</v>
@@ -16736,13 +16736,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
@@ -17665,13 +17665,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -17976,13 +17976,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
@@ -18020,11 +18020,11 @@
       <c r="U172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V172" s="9" t="n">
-        <v>1</v>
+      <c r="V172" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X172" s="10" t="n">
         <v>4</v>
@@ -19414,13 +19414,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>4</v>
       </c>
       <c r="W186" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X186" s="10" t="n">
         <v>7</v>
@@ -19761,7 +19761,7 @@
         <v>0</v>
       </c>
       <c r="S189" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T189" s="9" t="n">
         <v>0</v>
@@ -19830,13 +19830,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L190" s="7" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F191" s="6" t="n">
         <v>10</v>
@@ -19973,8 +19973,8 @@
       <c r="S191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T191" s="9" t="n">
-        <v>0</v>
+      <c r="T191" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U191" s="9" t="n">
         <v>0</v>
@@ -21385,13 +21385,13 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K205" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
@@ -21894,13 +21894,13 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J210" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L210" s="7" t="inlineStr">
         <is>
@@ -22096,13 +22096,13 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J212" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K212" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>4</v>
       </c>
       <c r="W212" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X212" s="10" t="n">
         <v>5</v>
@@ -22617,13 +22617,13 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K217" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>0</v>
       </c>
       <c r="V217" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W217" s="9" t="n">
         <v>0</v>
@@ -23011,7 +23011,7 @@
         </is>
       </c>
       <c r="E221" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F221" s="6" t="n">
         <v>10</v>
@@ -23066,8 +23066,8 @@
       <c r="T221" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U221" s="9" t="n">
-        <v>0</v>
+      <c r="U221" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V221" s="9" t="n">
         <v>3</v>
@@ -23130,13 +23130,13 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J222" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K222" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
@@ -23157,13 +23157,13 @@
         </is>
       </c>
       <c r="P222" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q222" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R222" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S222" s="9" t="n">
         <v>0</v>
@@ -23178,7 +23178,7 @@
         <v>4</v>
       </c>
       <c r="W222" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X222" s="10" t="n">
         <v>7</v>
@@ -23512,7 +23512,7 @@
         </is>
       </c>
       <c r="E226" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F226" s="6" t="n">
         <v>10</v>
@@ -23556,16 +23556,16 @@
         <v>3</v>
       </c>
       <c r="Q226" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R226" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S226" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T226" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T226" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U226" s="9" t="n">
         <v>0</v>
@@ -23661,7 +23661,7 @@
         <v>0</v>
       </c>
       <c r="S227" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T227" s="10" t="n">
         <v>1</v>
@@ -24222,10 +24222,10 @@
         <v>54</v>
       </c>
       <c r="J233" s="4" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K233" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L233" s="4" t="inlineStr">
         <is>
@@ -24417,13 +24417,13 @@
         </is>
       </c>
       <c r="I235" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J235" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K235" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L235" s="7" t="inlineStr">
         <is>
@@ -24813,13 +24813,13 @@
         </is>
       </c>
       <c r="I239" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J239" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K239" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L239" s="7" t="inlineStr">
         <is>
@@ -25011,13 +25011,13 @@
         </is>
       </c>
       <c r="I241" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K241" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L241" s="7" t="inlineStr">
         <is>
@@ -25311,10 +25311,10 @@
         <v>27</v>
       </c>
       <c r="J244" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K244" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -26484,13 +26484,13 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -26499,7 +26499,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -26550,7 +26550,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -26649,7 +26649,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -26781,7 +26781,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -26796,7 +26796,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -26961,7 +26961,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -27012,7 +27012,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -27078,7 +27078,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -27441,7 +27441,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -27606,7 +27606,7 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -27804,7 +27804,7 @@
         <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -27837,7 +27837,7 @@
         <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
